--- a/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="92">
   <si>
     <t>SEVN</t>
   </si>
@@ -656,112 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -774,77 +775,80 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E8" s="3">
         <v>7700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>26100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2000</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -857,8 +861,11 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -866,10 +873,10 @@
         <v>600</v>
       </c>
       <c r="E9" s="3">
+        <v>600</v>
+      </c>
+      <c r="F9" s="3">
         <v>500</v>
-      </c>
-      <c r="F9" s="3">
-        <v>600</v>
       </c>
       <c r="G9" s="3">
         <v>600</v>
@@ -893,41 +900,41 @@
         <v>600</v>
       </c>
       <c r="N9" s="3">
+        <v>600</v>
+      </c>
+      <c r="O9" s="3">
         <v>500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3">
         <v>8500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>700</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -940,77 +947,80 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E10" s="3">
         <v>7200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>12700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1300</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1023,8 +1033,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1054,8 +1067,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1137,8 +1151,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1220,8 +1237,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1264,8 +1284,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1277,11 +1297,11 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1297,14 +1317,17 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1333,17 +1356,17 @@
         <v>300</v>
       </c>
       <c r="L15" s="3">
+        <v>300</v>
+      </c>
+      <c r="M15" s="3">
         <v>400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>100</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1386,8 +1409,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1414,77 +1440,78 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E17" s="3">
         <v>3300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1600</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1497,77 +1524,80 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E18" s="3">
         <v>4400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>11200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>20900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>400</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1610,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1611,8 +1644,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1655,8 +1689,8 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1679,8 +1713,8 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
+      <c r="Y20" s="3">
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
@@ -1694,53 +1728,56 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E21" s="3">
         <v>4700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1750,12 +1787,12 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>21000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1777,8 +1814,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1821,8 +1861,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1860,77 +1900,80 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>4400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>11200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>21000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>400</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,8 +1986,11 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1976,11 +2022,11 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -2000,19 +2046,19 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
+      <c r="Y24" s="3">
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
@@ -2026,8 +2072,11 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2109,77 +2158,80 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>4400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>11100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>20700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>400</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,77 +2244,80 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>4300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>11100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>20700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>400</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2275,8 +2330,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2358,8 +2416,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2441,8 +2502,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2524,8 +2588,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2607,8 +2674,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2651,8 +2721,8 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -2675,8 +2745,8 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
+      <c r="Y32" s="3">
+        <v>0</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
@@ -2690,77 +2760,80 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
         <v>4400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>11100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>20700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>400</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2846,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2856,77 +2932,80 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
         <v>4400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>11100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>20700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>400</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2939,82 +3018,85 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3027,8 +3109,11 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3058,8 +3143,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3089,77 +3175,78 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E41" s="3">
         <v>56600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>123500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>77500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>46000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>41600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>70800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>82200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>69600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>93300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>87900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>60400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>81800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>84300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>71100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>76400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>48200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>26200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>19300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>30400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>46800</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3172,8 +3259,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3255,53 +3345,56 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>709600</v>
+      </c>
+      <c r="E43" s="3">
         <v>725200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>681300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>607000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>625900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>657000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>605900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>554000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>607800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>587800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>626400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>671800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>628800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>621300</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -3332,14 +3425,17 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
+      <c r="AB43" s="3">
+        <v>0</v>
       </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3382,8 +3478,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3421,77 +3517,80 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,53 +3603,56 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>781800</v>
+      </c>
+      <c r="E46" s="3">
         <v>783200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>806300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>687000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>673300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>700100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>677500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>637900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>679900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>682600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>715400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>733400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>712300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>706800</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3581,14 +3683,17 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
+      <c r="AB46" s="3">
+        <v>0</v>
       </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3631,33 +3736,33 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
         <v>669900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>695200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>670200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>622700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>572200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>436100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>211400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>147700</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3670,8 +3775,11 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3714,8 +3822,8 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -3753,8 +3861,11 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3836,8 +3947,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3919,8 +4033,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4002,76 +4119,79 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E52" s="3">
         <v>14200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15600</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>200</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>500</v>
-      </c>
-      <c r="W52" s="3">
-        <v>200</v>
       </c>
       <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
+      <c r="Y52" s="3">
+        <v>200</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
@@ -4079,14 +4199,17 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4168,77 +4291,80 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>795100</v>
+      </c>
+      <c r="E54" s="3">
         <v>797400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>820900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>700800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>687400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>714400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>692800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>652600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>694900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>697700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>731500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>750000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>727900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>706800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>746800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>775200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>721700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>635000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>600000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>456200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>244500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>195100</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4251,8 +4377,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4282,8 +4411,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4313,77 +4443,78 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2600</v>
       </c>
       <c r="I57" s="3">
         <v>2600</v>
       </c>
       <c r="J57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1100</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,41 +4527,44 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>135600</v>
+      </c>
+      <c r="E58" s="3">
         <v>135500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>423200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>352400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>236300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>244000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>213300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>330300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>333600</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4440,14 +4574,14 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -4479,58 +4613,61 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2400</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1800</v>
       </c>
       <c r="R59" s="3">
         <v>1800</v>
       </c>
       <c r="S59" s="3">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="T59" s="3">
         <v>1100</v>
@@ -4539,17 +4676,17 @@
         <v>1100</v>
       </c>
       <c r="V59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W59" s="3">
         <v>1700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>700</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4562,53 +4699,56 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>139500</v>
+      </c>
+      <c r="E60" s="3">
         <v>139900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>427500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>357000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>240400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>247900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>218400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>334100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>337300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5600</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4639,80 +4779,83 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
+      <c r="AB60" s="3">
+        <v>0</v>
       </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>334700</v>
+      </c>
+      <c r="E61" s="3">
         <v>330300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>64400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>77000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>179700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>196400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>417800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>162600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>87600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>87500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>454400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>473300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>452700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>433400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>471500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>503500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>452700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>367700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>339600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>215700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>48800</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4728,8 +4871,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4737,7 +4883,7 @@
         <v>200</v>
       </c>
       <c r="E62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F62" s="3">
         <v>300</v>
@@ -4746,23 +4892,23 @@
         <v>300</v>
       </c>
       <c r="H62" s="3">
+        <v>300</v>
+      </c>
+      <c r="I62" s="3">
         <v>1100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>2100</v>
       </c>
       <c r="K62" s="3">
         <v>2100</v>
       </c>
       <c r="L62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="M62" s="3">
         <v>1400</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4772,8 +4918,8 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -4805,14 +4951,17 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
+      <c r="AB62" s="3">
+        <v>0</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4894,8 +5043,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4977,8 +5129,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5060,77 +5215,80 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>474500</v>
+      </c>
+      <c r="E66" s="3">
         <v>470400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>492200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>434400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>420400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>445500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>423500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>383100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>423800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>426200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>460300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>479700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>460100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>439000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>475300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>506800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>455000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>369800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>342300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>219600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>51400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1800</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5143,8 +5301,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5174,8 +5335,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5257,8 +5419,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5340,8 +5505,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5423,8 +5591,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5506,77 +5677,80 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E72" s="3">
         <v>23500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>24900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>28800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>29200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>30900</v>
-      </c>
-      <c r="L72" s="3">
-        <v>31800</v>
       </c>
       <c r="M72" s="3">
         <v>31800</v>
       </c>
       <c r="N72" s="3">
+        <v>31800</v>
+      </c>
+      <c r="O72" s="3">
         <v>30900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>28600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>29100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>33100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>30000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>28500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>27500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>20100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-600</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
-      </c>
       <c r="X72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="3">
         <v>400</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5589,8 +5763,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5672,8 +5849,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5755,8 +5935,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5838,77 +6021,80 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>320700</v>
+      </c>
+      <c r="E76" s="3">
         <v>327000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>328700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>266500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>267000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>268900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>269300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>269500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>271100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>271600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>271200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>270300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>267800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>267700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>271600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>268400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>266700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>265300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>257700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>236600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>193100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>193200</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5921,8 +6107,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6004,82 +6193,85 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6092,77 +6284,80 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
         <v>4400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>11100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>20700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>400</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6175,8 +6370,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6206,8 +6404,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6224,16 +6423,16 @@
         <v>300</v>
       </c>
       <c r="H83" s="3">
+        <v>300</v>
+      </c>
+      <c r="I83" s="3">
         <v>400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>300</v>
       </c>
       <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3">
+        <v>300</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -6259,8 +6458,8 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -6289,8 +6488,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6372,8 +6574,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6455,8 +6660,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6538,8 +6746,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6621,8 +6832,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6704,77 +6918,80 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E89" s="3">
         <v>5000</v>
-      </c>
-      <c r="E89" s="3">
-        <v>3200</v>
       </c>
       <c r="F89" s="3">
         <v>3200</v>
       </c>
       <c r="G89" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H89" s="3">
         <v>5000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6787,8 +7004,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6818,8 +7038,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6862,8 +7083,8 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -6901,8 +7122,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6984,8 +7208,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7067,77 +7294,80 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-43600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-72600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>20100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>29500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-49900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-52300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>53100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>39600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>46500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-39900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-21100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>50300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>27800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-44900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-44600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-116800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-49000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-63000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7150,8 +7380,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7181,8 +7414,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7190,13 +7424,13 @@
         <v>6300</v>
       </c>
       <c r="E96" s="3">
-        <v>4200</v>
+        <v>6300</v>
       </c>
       <c r="F96" s="3">
         <v>4200</v>
       </c>
       <c r="G96" s="3">
-        <v>5200</v>
+        <v>4200</v>
       </c>
       <c r="H96" s="3">
         <v>5200</v>
@@ -7220,32 +7454,32 @@
         <v>5200</v>
       </c>
       <c r="O96" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="P96" s="3">
         <v>5100</v>
       </c>
       <c r="Q96" s="3">
-        <v>-3700</v>
+        <v>5100</v>
       </c>
       <c r="R96" s="3">
         <v>-3700</v>
       </c>
       <c r="S96" s="3">
-        <v>-3600</v>
+        <v>-3700</v>
       </c>
       <c r="T96" s="3">
         <v>-3600</v>
       </c>
       <c r="U96" s="3">
-        <v>0</v>
+        <v>-3600</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-3100</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -7264,8 +7498,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7347,8 +7584,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7430,8 +7670,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7513,77 +7756,80 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-28300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>115400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>8300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-30100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>17100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>37000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-47800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-38800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-24500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>15000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>13800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-43600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-36000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>46700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>81100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>24200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>123700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>34900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>47300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7596,8 +7842,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7640,8 +7889,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7679,77 +7928,80 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-66900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>46000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>31500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-29100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-23700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>27300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-21500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>13200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>28000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>39400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-17300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-10800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-16500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-56500</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7760,6 +8012,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
